--- a/test-data/Sample_BarSetupProduct.xlsx
+++ b/test-data/Sample_BarSetupProduct.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="308">
   <si>
     <t xml:space="preserve">BarSetup Product Name</t>
   </si>
@@ -70,7 +70,7 @@
     <t xml:space="preserve">Bristol Corporate Bar Setup</t>
   </si>
   <si>
-    <t xml:space="preserve">Apple Juice</t>
+    <t xml:space="preserve">ChillBuzz </t>
   </si>
   <si>
     <t xml:space="preserve">1liter</t>
@@ -80,6 +80,870 @@
   </si>
   <si>
     <t xml:space="preserve">Sonam Burbure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeonSip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FrostFuel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sipster </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BuzzDrop </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiquidVibe </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChillWave </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlowSip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IceRush</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velvet Pour </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golden Elixir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Royal Sip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crystal Blend </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqua Vibe </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zing+ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luxe Liquid </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imperial Pour </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elite Essence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noble Sip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FreshFizz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zing Splash </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citrus Pop </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cool Breeze </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minty Magic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fruity Fusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sparkle Sip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berry Blast </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lemon Chill </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tropical Twist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green Glow </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detox Drop </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pure Press </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vita Juice </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh Flow </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nature Sip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fruit Pulse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Healthy Boost </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean Sip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energy Elixir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoolQuench </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZestSplash </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AquaVibe </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChillDrop </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PureSip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FrostyFlow </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SplashMint </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrispWave </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HydroZing </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berry Bliss </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citrus Spark </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mango Mist </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peachy Pour </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tropical Twist </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lemon Glow </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pineapple </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple Zing </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guava Rush </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orange Splash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VitaFresh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detox Dew </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbal Chill </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh Roots </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Squeeze </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NutriSip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZenDrop </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IceNova </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChillAura </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FrostNova </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiquidZen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coolify </t>
+  </si>
+  <si>
+    <t xml:space="preserve">UrbanSip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoDrink </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sipora </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydrolux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refreshix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elixia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aquora </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veloura Sip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenvy Drinks </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purevia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frescura </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydravia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nourix </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitalora </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Essentia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zest </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sipzy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FizzUp </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dripo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sippa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quench </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuno </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glint </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viro </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pure Refresh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clear Sip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqua Prime </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh Essence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crystal Hydrate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classic Quench </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refined Sip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium Pour </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vital Refresh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elite Hydration </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydrate Pro </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqua Core </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RefreshPoint </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ClearFlow </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PureStream </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VitaCore </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AquaLine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RefreshEdge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HydroPoint </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoreSip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green Essence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural Flow </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pure Balance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh Harmony </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean Hydrate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vital Blend </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nature Core </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zen Refresh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calm Sip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanced Drop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AquaNova </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refreshix </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ClearNova </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoSip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flowra </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydrion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freshix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lemon Refresh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mint Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citrus Water </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh Lime Soda </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berry Refresher </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orange Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coconut Water Fresh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iced Herbal Drink </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixed Fruit Refresher </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqua Select </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pure Hydrate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clear Essence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh Protocol </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prime Hydration </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Still Refresh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crisp Reserve </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluid Balance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily Hydrate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard Sip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boardroom Brew (non-alcoholic) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting Mint </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workday Refresher </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office Oasis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Executive Hydrate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporate Quencher </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Sip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focus Fuel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Productivity Pour </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desk Refresh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simply Fresh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mild Citrus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light Zing </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soft Splash </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gentle Mint </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pure Infusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean Citrus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtle Berry </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural Infuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh Blend </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HydroSphere </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AquaShift </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ClearEdge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RefreshLab </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluidix </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aquafy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydronex </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streamix </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlowCore </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pureon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature Infusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classic Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium Refresher </t>
+  </si>
+  <si>
+    <t xml:space="preserve">House Hydrate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Special Blend </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh Selection </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature Citrus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crafted Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refined Refresh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lemon Infusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mint Infused Water </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citrus Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berry Infusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ginger Fresh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple Mint Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orange Infusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbal Lemon Drink </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cucumber Mint Water </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basil Lemon Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platinum Refresh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Executive Infusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature Reserve (Non-Alcoholic) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elite Hydrate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prestige Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prime Infusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporate Reserve </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium Essence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director’s Refresh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select Infusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elderflower Refresher </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lemon &amp; Mint Press </t>
+  </si>
+  <si>
+    <t xml:space="preserve">English Garden Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citrus Spritz (Non-Alcoholic) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple &amp; Elderflower Sparkle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traditional Lemonade </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh Lime &amp; Soda </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raspberry Refresher </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cucumber Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orchard Apple Drink </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pure Hydration </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clear Refreshment </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Still Citrus Blend </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sparkling Citrus Water </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh Lime Infusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classic Lemon Refresher </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citrus Hydrate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural Fruit Blend </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filtered Fresh Drink </t>
+  </si>
+  <si>
+    <t xml:space="preserve">House Refresher </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature Hydration </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium Citrus Drink </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily Refreshment </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh Infusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature Blend </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chilled Refreshment </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light Fruit Cooler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gentle Citrus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light Mint Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soft Fruit Infusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanced Refresh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural Citrus Water </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mild Berry Blend </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delicate Lemon Drink </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh Botanical Infusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pure Fruit Essence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqua Refresh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydro Blend </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ClearFlow Drink </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refresh Core </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqua Balance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PureStream Drink </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FreshLine Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydro Essence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqua Classic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluid Refresh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lemon Water </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mint Water </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citrus Drink </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple Juice </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orange Juice </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixed Fruit Juice </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coconut Water </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sparkling Water </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Still Water </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fruit Infus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Executive Refresher </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platinum Hydration </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature Citrus Infusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elite Fresh Blend </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium Fruit Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refined Refreshment </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporate Signature Drink </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classic Premium Cooler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select Fruit Infusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zesty Zing </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sip Happens </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Just Chill </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slay Sip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydrate Mate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sip Pop </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chillax Juice </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sippin’ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydrate+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlowUp Drink </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chill+</t>
   </si>
 </sst>
 </file>
@@ -89,7 +953,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -118,6 +982,18 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -162,13 +1038,29 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -423,87 +1315,6944 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O300"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="21.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="18.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="21.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="4.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="29.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="21.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="4.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="29.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="16.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="A2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" s="0" t="s">
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J31" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J43" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J44" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J49" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J51" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J58" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J59" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J60" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J63" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J64" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J65" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J69" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J73" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J74" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J75" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J76" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J77" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J78" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J79" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J80" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J81" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O81" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J82" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J83" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O83" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J84" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O84" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J85" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O85" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O86" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J87" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O87" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J88" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O88" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J89" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J91" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O91" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J92" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O92" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J93" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O93" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J94" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J95" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O95" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J96" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O96" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J97" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O97" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J98" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O98" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J99" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O99" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J100" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O100" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J101" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O101" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J102" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O102" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J103" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O103" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J104" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O104" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J105" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O105" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J106" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O106" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J107" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O107" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J108" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O108" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J109" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O109" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J110" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O110" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J111" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O111" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J112" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O112" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J113" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O113" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J114" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O114" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J115" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O115" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J116" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O116" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O117" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J118" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O118" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J119" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O119" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J120" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O120" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J121" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O121" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J122" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O122" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J123" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O123" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J124" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O124" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J125" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O125" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J126" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O126" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O127" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O128" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J129" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O129" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J130" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O130" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J131" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O131" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J132" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O132" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J133" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O133" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J134" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O134" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J135" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O135" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J136" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O136" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A137" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J137" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O137" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A138" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J138" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O138" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A139" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J139" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O139" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A140" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J140" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O140" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J141" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O141" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J142" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O142" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J143" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O143" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A144" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J144" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O144" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J145" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O145" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J146" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O146" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A147" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J147" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O147" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J148" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O148" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A149" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J149" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O149" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J150" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O150" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A151" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J151" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O151" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J152" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O152" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J153" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O153" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A154" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J154" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O154" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J155" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O155" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J156" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O156" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A157" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J157" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O157" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A158" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J158" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O158" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A159" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J159" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O159" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A160" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J160" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O160" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A161" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J161" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O161" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A162" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J162" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O162" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A163" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J163" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O163" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A164" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J164" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O164" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A165" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J165" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O165" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A166" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J166" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O166" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A167" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J167" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O167" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A168" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J168" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O168" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A169" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J169" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O169" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A170" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J170" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O170" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A171" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J171" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O171" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A172" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J172" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O172" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A173" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J173" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O173" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A174" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J174" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O174" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A175" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J175" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O175" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A176" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J176" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O176" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A177" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J177" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O177" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A178" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J178" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O178" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A179" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J179" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O179" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A180" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J180" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O180" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A181" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J181" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O181" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A182" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J182" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O182" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A183" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J183" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O183" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A184" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J184" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O184" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A185" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J185" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O185" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A186" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J186" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O186" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A187" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J187" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O187" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A188" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J188" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O188" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A189" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J189" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O189" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A190" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J190" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O190" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A191" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J191" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O191" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A192" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J192" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O192" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A193" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J193" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O193" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A194" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J194" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O194" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A195" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J195" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O195" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A196" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J196" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O196" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A197" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J197" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O197" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A198" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J198" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O198" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A199" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J199" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O199" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A200" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J200" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O200" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A201" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J201" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O201" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A202" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J202" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O202" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A203" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J203" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O203" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A204" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J204" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O204" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A205" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J205" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O205" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A206" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J206" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O206" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A207" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J207" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O207" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A208" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J208" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O208" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A209" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J209" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O209" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A210" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J210" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O210" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A211" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J211" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O211" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A212" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J212" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O212" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A213" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J213" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O213" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A214" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J214" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O214" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A215" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J215" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O215" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A216" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J216" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O216" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A217" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J217" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O217" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A218" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J218" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O218" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A219" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J219" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O219" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A220" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J220" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O220" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A221" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J221" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O221" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A222" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J222" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O222" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A223" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J223" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O223" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A224" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J224" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O224" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A225" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J225" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O225" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A226" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J226" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O226" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A227" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F227" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J227" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O227" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A228" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F228" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J228" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O228" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A229" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F229" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J229" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O229" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A230" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F230" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J230" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O230" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A231" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J231" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O231" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A232" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F232" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J232" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O232" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A233" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J233" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O233" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A234" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J234" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O234" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A235" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F235" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J235" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O235" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A236" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F236" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J236" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O236" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A237" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F237" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J237" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O237" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A238" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F238" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J238" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O238" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A239" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F239" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J239" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O239" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A240" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F240" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J240" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O240" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A241" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F241" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J241" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O241" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A242" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F242" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J242" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O242" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A243" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F243" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J243" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O243" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A244" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F244" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J244" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O244" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A245" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F245" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J245" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O245" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A246" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F246" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J246" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O246" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A247" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F247" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J247" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O247" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A248" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F248" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J248" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O248" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A249" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F249" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J249" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O249" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A250" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F250" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J250" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O250" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A251" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F251" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J251" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O251" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A252" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F252" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J252" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O252" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A253" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F253" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J253" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O253" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A254" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F254" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J254" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O254" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A255" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F255" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J255" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O255" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A256" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F256" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J256" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O256" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A257" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F257" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J257" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O257" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A258" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F258" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J258" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O258" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A259" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F259" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J259" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O259" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A260" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F260" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J260" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O260" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A261" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F261" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J261" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O261" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A262" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F262" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J262" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O262" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A263" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F263" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J263" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O263" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A264" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F264" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J264" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O264" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A265" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F265" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J265" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O265" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A266" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F266" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J266" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O266" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A267" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F267" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J267" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O267" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A268" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F268" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J268" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O268" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A269" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F269" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J269" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O269" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A270" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F270" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J270" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O270" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A271" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F271" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J271" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O271" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A272" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F272" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J272" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O272" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="273" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A273" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F273" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J273" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O273" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="274" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A274" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F274" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J274" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O274" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A275" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C275" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F275" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J275" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O275" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="276" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A276" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F276" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J276" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O276" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="277" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A277" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C277" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F277" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J277" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O277" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="278" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A278" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F278" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J278" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O278" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="279" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A279" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="E279" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F279" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J279" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O279" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="280" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A280" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F280" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J280" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O280" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="281" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A281" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C281" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="E281" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F281" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J281" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O281" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A282" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="E282" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F282" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J282" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O282" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="283" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A283" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="E283" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F283" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J283" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O283" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="284" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A284" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C284" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E284" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F284" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J284" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O284" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A285" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C285" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F285" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J285" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O285" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="286" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A286" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B286" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C286" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F286" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J286" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O286" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="287" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A287" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B287" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C287" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F287" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J287" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O287" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="288" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A288" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B288" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C288" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F288" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J288" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O288" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="289" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A289" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B289" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C289" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F289" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J289" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O289" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="290" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A290" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B290" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E290" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F290" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J290" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O290" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="291" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A291" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C291" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="E291" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F291" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J291" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O291" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="292" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A292" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C292" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="E292" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F292" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J292" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O292" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A293" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C293" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E293" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F293" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J293" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O293" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A294" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C294" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="E294" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F294" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J294" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O294" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="295" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A295" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C295" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E295" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F295" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J295" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O295" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="296" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A296" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="E296" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F296" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J296" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O296" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="297" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A297" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B297" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C297" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="E297" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F297" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J297" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O297" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="298" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A298" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B298" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C298" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="E298" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F298" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J298" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O298" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="299" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A299" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B299" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C299" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="E299" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F299" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J299" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O299" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="300" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A300" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B300" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C300" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="E300" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F300" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J300" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O300" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/test-data/Sample_BarSetupProduct.xlsx
+++ b/test-data/Sample_BarSetupProduct.xlsx
@@ -73,7 +73,7 @@
     <t xml:space="preserve">ChillBuzz </t>
   </si>
   <si>
-    <t xml:space="preserve">1liter</t>
+    <t xml:space="preserve">2 liter</t>
   </si>
   <si>
     <t xml:space="preserve">ml</t>
@@ -953,7 +953,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -984,16 +984,11 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1051,15 +1046,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1315,7 +1310,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O300"/>
+  <dimension ref="A1:O360"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.85"/>
@@ -1389,7 +1384,7 @@
       <c r="C2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -1412,7 +1407,7 @@
       <c r="C3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -1435,7 +1430,7 @@
       <c r="C4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -1458,7 +1453,7 @@
       <c r="C5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -1481,7 +1476,7 @@
       <c r="C6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -1504,7 +1499,7 @@
       <c r="C7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -1527,7 +1522,7 @@
       <c r="C8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -1550,7 +1545,7 @@
       <c r="C9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -1573,7 +1568,7 @@
       <c r="C10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -1596,7 +1591,7 @@
       <c r="C11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -1619,7 +1614,7 @@
       <c r="C12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -1642,7 +1637,7 @@
       <c r="C13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -1665,7 +1660,7 @@
       <c r="C14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -1688,7 +1683,7 @@
       <c r="C15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -1711,7 +1706,7 @@
       <c r="C16" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -1734,7 +1729,7 @@
       <c r="C17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -1757,7 +1752,7 @@
       <c r="C18" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -1780,7 +1775,7 @@
       <c r="C19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F19" s="1" t="s">
@@ -1803,7 +1798,7 @@
       <c r="C20" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F20" s="1" t="s">
@@ -1826,7 +1821,7 @@
       <c r="C21" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -1849,7 +1844,7 @@
       <c r="C22" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F22" s="1" t="s">
@@ -1872,7 +1867,7 @@
       <c r="C23" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F23" s="1" t="s">
@@ -1895,7 +1890,7 @@
       <c r="C24" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -1918,7 +1913,7 @@
       <c r="C25" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -1941,7 +1936,7 @@
       <c r="C26" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F26" s="1" t="s">
@@ -1964,7 +1959,7 @@
       <c r="C27" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -1987,7 +1982,7 @@
       <c r="C28" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -2010,7 +2005,7 @@
       <c r="C29" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F29" s="1" t="s">
@@ -2033,7 +2028,7 @@
       <c r="C30" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F30" s="1" t="s">
@@ -2056,7 +2051,7 @@
       <c r="C31" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F31" s="1" t="s">
@@ -2079,7 +2074,7 @@
       <c r="C32" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -2102,7 +2097,7 @@
       <c r="C33" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F33" s="1" t="s">
@@ -2125,7 +2120,7 @@
       <c r="C34" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F34" s="1" t="s">
@@ -2148,7 +2143,7 @@
       <c r="C35" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F35" s="1" t="s">
@@ -2171,7 +2166,7 @@
       <c r="C36" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -2194,7 +2189,7 @@
       <c r="C37" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F37" s="1" t="s">
@@ -2217,7 +2212,7 @@
       <c r="C38" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F38" s="1" t="s">
@@ -2240,7 +2235,7 @@
       <c r="C39" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F39" s="1" t="s">
@@ -2263,7 +2258,7 @@
       <c r="C40" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -2286,7 +2281,7 @@
       <c r="C41" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F41" s="1" t="s">
@@ -2309,7 +2304,7 @@
       <c r="C42" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -2332,7 +2327,7 @@
       <c r="C43" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F43" s="1" t="s">
@@ -2355,7 +2350,7 @@
       <c r="C44" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F44" s="1" t="s">
@@ -2378,7 +2373,7 @@
       <c r="C45" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F45" s="1" t="s">
@@ -2401,7 +2396,7 @@
       <c r="C46" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -2424,7 +2419,7 @@
       <c r="C47" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F47" s="1" t="s">
@@ -2447,7 +2442,7 @@
       <c r="C48" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F48" s="1" t="s">
@@ -2470,7 +2465,7 @@
       <c r="C49" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F49" s="1" t="s">
@@ -2493,7 +2488,7 @@
       <c r="C50" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F50" s="1" t="s">
@@ -2516,7 +2511,7 @@
       <c r="C51" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F51" s="1" t="s">
@@ -2539,7 +2534,7 @@
       <c r="C52" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F52" s="1" t="s">
@@ -2562,7 +2557,7 @@
       <c r="C53" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F53" s="1" t="s">
@@ -2585,7 +2580,7 @@
       <c r="C54" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F54" s="1" t="s">
@@ -2608,7 +2603,7 @@
       <c r="C55" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F55" s="1" t="s">
@@ -2631,7 +2626,7 @@
       <c r="C56" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F56" s="1" t="s">
@@ -2654,7 +2649,7 @@
       <c r="C57" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F57" s="1" t="s">
@@ -2677,7 +2672,7 @@
       <c r="C58" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F58" s="1" t="s">
@@ -2700,7 +2695,7 @@
       <c r="C59" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F59" s="1" t="s">
@@ -2723,7 +2718,7 @@
       <c r="C60" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E60" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F60" s="1" t="s">
@@ -2746,7 +2741,7 @@
       <c r="C61" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E61" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F61" s="1" t="s">
@@ -2769,7 +2764,7 @@
       <c r="C62" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F62" s="1" t="s">
@@ -2792,7 +2787,7 @@
       <c r="C63" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F63" s="1" t="s">
@@ -2815,7 +2810,7 @@
       <c r="C64" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F64" s="1" t="s">
@@ -2838,7 +2833,7 @@
       <c r="C65" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F65" s="1" t="s">
@@ -2861,7 +2856,7 @@
       <c r="C66" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E66" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F66" s="1" t="s">
@@ -2884,7 +2879,7 @@
       <c r="C67" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E67" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F67" s="1" t="s">
@@ -2907,7 +2902,7 @@
       <c r="C68" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E68" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F68" s="1" t="s">
@@ -2930,7 +2925,7 @@
       <c r="C69" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E69" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F69" s="1" t="s">
@@ -2953,7 +2948,7 @@
       <c r="C70" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E70" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F70" s="1" t="s">
@@ -2976,7 +2971,7 @@
       <c r="C71" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E71" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F71" s="1" t="s">
@@ -2999,7 +2994,7 @@
       <c r="C72" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E72" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F72" s="1" t="s">
@@ -3022,7 +3017,7 @@
       <c r="C73" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E73" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F73" s="1" t="s">
@@ -3045,7 +3040,7 @@
       <c r="C74" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E74" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F74" s="1" t="s">
@@ -3068,7 +3063,7 @@
       <c r="C75" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E75" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F75" s="1" t="s">
@@ -3091,7 +3086,7 @@
       <c r="C76" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E76" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F76" s="1" t="s">
@@ -3114,7 +3109,7 @@
       <c r="C77" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E77" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F77" s="1" t="s">
@@ -3137,7 +3132,7 @@
       <c r="C78" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E78" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F78" s="1" t="s">
@@ -3160,7 +3155,7 @@
       <c r="C79" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="E79" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F79" s="1" t="s">
@@ -3183,7 +3178,7 @@
       <c r="C80" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E80" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F80" s="1" t="s">
@@ -3206,7 +3201,7 @@
       <c r="C81" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E81" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F81" s="1" t="s">
@@ -3229,7 +3224,7 @@
       <c r="C82" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E82" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F82" s="1" t="s">
@@ -3252,7 +3247,7 @@
       <c r="C83" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E83" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F83" s="1" t="s">
@@ -3275,7 +3270,7 @@
       <c r="C84" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E84" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F84" s="1" t="s">
@@ -3298,7 +3293,7 @@
       <c r="C85" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E85" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F85" s="1" t="s">
@@ -3321,7 +3316,7 @@
       <c r="C86" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E86" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F86" s="1" t="s">
@@ -3344,7 +3339,7 @@
       <c r="C87" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E87" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F87" s="1" t="s">
@@ -3367,7 +3362,7 @@
       <c r="C88" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E88" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F88" s="1" t="s">
@@ -3390,7 +3385,7 @@
       <c r="C89" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="E89" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F89" s="1" t="s">
@@ -3413,7 +3408,7 @@
       <c r="C90" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="E90" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F90" s="1" t="s">
@@ -3436,7 +3431,7 @@
       <c r="C91" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E91" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F91" s="1" t="s">
@@ -3459,7 +3454,7 @@
       <c r="C92" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E92" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F92" s="1" t="s">
@@ -3482,7 +3477,7 @@
       <c r="C93" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="E93" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F93" s="1" t="s">
@@ -3505,7 +3500,7 @@
       <c r="C94" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="E94" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F94" s="1" t="s">
@@ -3528,7 +3523,7 @@
       <c r="C95" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E95" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F95" s="1" t="s">
@@ -3551,7 +3546,7 @@
       <c r="C96" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="E96" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F96" s="1" t="s">
@@ -3574,7 +3569,7 @@
       <c r="C97" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E97" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F97" s="1" t="s">
@@ -3597,7 +3592,7 @@
       <c r="C98" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E98" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F98" s="1" t="s">
@@ -3620,7 +3615,7 @@
       <c r="C99" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E99" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F99" s="1" t="s">
@@ -3643,7 +3638,7 @@
       <c r="C100" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="E100" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F100" s="1" t="s">
@@ -3666,7 +3661,7 @@
       <c r="C101" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E101" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F101" s="1" t="s">
@@ -3689,7 +3684,7 @@
       <c r="C102" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E102" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F102" s="1" t="s">
@@ -3712,7 +3707,7 @@
       <c r="C103" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="E103" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F103" s="1" t="s">
@@ -3735,7 +3730,7 @@
       <c r="C104" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E104" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F104" s="1" t="s">
@@ -3758,7 +3753,7 @@
       <c r="C105" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E105" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F105" s="1" t="s">
@@ -3781,7 +3776,7 @@
       <c r="C106" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="E106" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F106" s="1" t="s">
@@ -3804,7 +3799,7 @@
       <c r="C107" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="E107" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F107" s="1" t="s">
@@ -3827,7 +3822,7 @@
       <c r="C108" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="E108" s="1" t="s">
+      <c r="E108" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F108" s="1" t="s">
@@ -3850,7 +3845,7 @@
       <c r="C109" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="E109" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F109" s="1" t="s">
@@ -3873,7 +3868,7 @@
       <c r="C110" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E110" s="1" t="s">
+      <c r="E110" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F110" s="1" t="s">
@@ -3896,7 +3891,7 @@
       <c r="C111" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E111" s="1" t="s">
+      <c r="E111" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F111" s="1" t="s">
@@ -3919,7 +3914,7 @@
       <c r="C112" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E112" s="1" t="s">
+      <c r="E112" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F112" s="1" t="s">
@@ -3942,7 +3937,7 @@
       <c r="C113" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="E113" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F113" s="1" t="s">
@@ -3965,7 +3960,7 @@
       <c r="C114" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E114" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F114" s="1" t="s">
@@ -3988,7 +3983,7 @@
       <c r="C115" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="E115" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F115" s="1" t="s">
@@ -4011,7 +4006,7 @@
       <c r="C116" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="E116" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F116" s="1" t="s">
@@ -4034,7 +4029,7 @@
       <c r="C117" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E117" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F117" s="1" t="s">
@@ -4057,7 +4052,7 @@
       <c r="C118" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="E118" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F118" s="1" t="s">
@@ -4080,7 +4075,7 @@
       <c r="C119" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E119" s="1" t="s">
+      <c r="E119" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F119" s="1" t="s">
@@ -4103,7 +4098,7 @@
       <c r="C120" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E120" s="1" t="s">
+      <c r="E120" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F120" s="1" t="s">
@@ -4126,7 +4121,7 @@
       <c r="C121" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="E121" s="1" t="s">
+      <c r="E121" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F121" s="1" t="s">
@@ -4149,7 +4144,7 @@
       <c r="C122" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E122" s="1" t="s">
+      <c r="E122" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F122" s="1" t="s">
@@ -4172,7 +4167,7 @@
       <c r="C123" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="E123" s="1" t="s">
+      <c r="E123" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F123" s="1" t="s">
@@ -4195,7 +4190,7 @@
       <c r="C124" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E124" s="1" t="s">
+      <c r="E124" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F124" s="1" t="s">
@@ -4218,7 +4213,7 @@
       <c r="C125" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E125" s="1" t="s">
+      <c r="E125" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F125" s="1" t="s">
@@ -4241,7 +4236,7 @@
       <c r="C126" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E126" s="1" t="s">
+      <c r="E126" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F126" s="1" t="s">
@@ -4264,7 +4259,7 @@
       <c r="C127" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="E127" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F127" s="1" t="s">
@@ -4287,7 +4282,7 @@
       <c r="C128" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E128" s="1" t="s">
+      <c r="E128" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F128" s="1" t="s">
@@ -4310,7 +4305,7 @@
       <c r="C129" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="E129" s="1" t="s">
+      <c r="E129" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F129" s="1" t="s">
@@ -4333,7 +4328,7 @@
       <c r="C130" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E130" s="1" t="s">
+      <c r="E130" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F130" s="1" t="s">
@@ -4356,7 +4351,7 @@
       <c r="C131" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="E131" s="1" t="s">
+      <c r="E131" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F131" s="1" t="s">
@@ -4379,7 +4374,7 @@
       <c r="C132" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E132" s="1" t="s">
+      <c r="E132" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F132" s="1" t="s">
@@ -4402,7 +4397,7 @@
       <c r="C133" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E133" s="1" t="s">
+      <c r="E133" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F133" s="1" t="s">
@@ -4425,7 +4420,7 @@
       <c r="C134" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E134" s="1" t="s">
+      <c r="E134" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F134" s="1" t="s">
@@ -4448,7 +4443,7 @@
       <c r="C135" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="E135" s="1" t="s">
+      <c r="E135" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F135" s="1" t="s">
@@ -4471,7 +4466,7 @@
       <c r="C136" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="E136" s="1" t="s">
+      <c r="E136" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F136" s="1" t="s">
@@ -4494,7 +4489,7 @@
       <c r="C137" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E137" s="1" t="s">
+      <c r="E137" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F137" s="1" t="s">
@@ -4517,7 +4512,7 @@
       <c r="C138" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="E138" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F138" s="1" t="s">
@@ -4540,7 +4535,7 @@
       <c r="C139" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="E139" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F139" s="1" t="s">
@@ -4563,7 +4558,7 @@
       <c r="C140" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="E140" s="1" t="s">
+      <c r="E140" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F140" s="1" t="s">
@@ -4586,7 +4581,7 @@
       <c r="C141" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E141" s="1" t="s">
+      <c r="E141" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F141" s="1" t="s">
@@ -4609,7 +4604,7 @@
       <c r="C142" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E142" s="1" t="s">
+      <c r="E142" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F142" s="1" t="s">
@@ -4632,7 +4627,7 @@
       <c r="C143" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="E143" s="1" t="s">
+      <c r="E143" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F143" s="1" t="s">
@@ -4655,7 +4650,7 @@
       <c r="C144" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E144" s="1" t="s">
+      <c r="E144" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F144" s="1" t="s">
@@ -4678,7 +4673,7 @@
       <c r="C145" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="E145" s="1" t="s">
+      <c r="E145" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F145" s="1" t="s">
@@ -4701,7 +4696,7 @@
       <c r="C146" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E146" s="1" t="s">
+      <c r="E146" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F146" s="1" t="s">
@@ -4724,7 +4719,7 @@
       <c r="C147" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="E147" s="1" t="s">
+      <c r="E147" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F147" s="1" t="s">
@@ -4747,7 +4742,7 @@
       <c r="C148" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E148" s="1" t="s">
+      <c r="E148" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F148" s="1" t="s">
@@ -4770,7 +4765,7 @@
       <c r="C149" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E149" s="1" t="s">
+      <c r="E149" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F149" s="1" t="s">
@@ -4793,7 +4788,7 @@
       <c r="C150" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="E150" s="1" t="s">
+      <c r="E150" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F150" s="1" t="s">
@@ -4816,7 +4811,7 @@
       <c r="C151" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="E151" s="1" t="s">
+      <c r="E151" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F151" s="1" t="s">
@@ -4839,7 +4834,7 @@
       <c r="C152" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E152" s="1" t="s">
+      <c r="E152" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F152" s="1" t="s">
@@ -4862,7 +4857,7 @@
       <c r="C153" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E153" s="1" t="s">
+      <c r="E153" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F153" s="1" t="s">
@@ -4885,7 +4880,7 @@
       <c r="C154" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="E154" s="1" t="s">
+      <c r="E154" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F154" s="1" t="s">
@@ -4908,7 +4903,7 @@
       <c r="C155" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E155" s="1" t="s">
+      <c r="E155" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F155" s="1" t="s">
@@ -4931,7 +4926,7 @@
       <c r="C156" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="E156" s="1" t="s">
+      <c r="E156" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F156" s="1" t="s">
@@ -4954,7 +4949,7 @@
       <c r="C157" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E157" s="1" t="s">
+      <c r="E157" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F157" s="1" t="s">
@@ -4977,7 +4972,7 @@
       <c r="C158" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E158" s="1" t="s">
+      <c r="E158" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F158" s="1" t="s">
@@ -5000,7 +4995,7 @@
       <c r="C159" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="E159" s="1" t="s">
+      <c r="E159" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F159" s="1" t="s">
@@ -5023,7 +5018,7 @@
       <c r="C160" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E160" s="1" t="s">
+      <c r="E160" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F160" s="1" t="s">
@@ -5046,7 +5041,7 @@
       <c r="C161" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E161" s="1" t="s">
+      <c r="E161" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F161" s="1" t="s">
@@ -5069,7 +5064,7 @@
       <c r="C162" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E162" s="1" t="s">
+      <c r="E162" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F162" s="1" t="s">
@@ -5092,7 +5087,7 @@
       <c r="C163" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E163" s="1" t="s">
+      <c r="E163" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F163" s="1" t="s">
@@ -5115,7 +5110,7 @@
       <c r="C164" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="E164" s="1" t="s">
+      <c r="E164" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F164" s="1" t="s">
@@ -5138,7 +5133,7 @@
       <c r="C165" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E165" s="1" t="s">
+      <c r="E165" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F165" s="1" t="s">
@@ -5161,7 +5156,7 @@
       <c r="C166" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="E166" s="1" t="s">
+      <c r="E166" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F166" s="1" t="s">
@@ -5184,7 +5179,7 @@
       <c r="C167" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E167" s="1" t="s">
+      <c r="E167" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F167" s="1" t="s">
@@ -5207,7 +5202,7 @@
       <c r="C168" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="E168" s="1" t="s">
+      <c r="E168" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F168" s="1" t="s">
@@ -5230,7 +5225,7 @@
       <c r="C169" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="E169" s="1" t="s">
+      <c r="E169" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F169" s="1" t="s">
@@ -5253,7 +5248,7 @@
       <c r="C170" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="E170" s="1" t="s">
+      <c r="E170" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F170" s="1" t="s">
@@ -5276,7 +5271,7 @@
       <c r="C171" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="E171" s="1" t="s">
+      <c r="E171" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F171" s="1" t="s">
@@ -5299,7 +5294,7 @@
       <c r="C172" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E172" s="1" t="s">
+      <c r="E172" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F172" s="1" t="s">
@@ -5322,7 +5317,7 @@
       <c r="C173" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="E173" s="1" t="s">
+      <c r="E173" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F173" s="1" t="s">
@@ -5345,7 +5340,7 @@
       <c r="C174" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="E174" s="1" t="s">
+      <c r="E174" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F174" s="1" t="s">
@@ -5368,7 +5363,7 @@
       <c r="C175" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E175" s="1" t="s">
+      <c r="E175" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F175" s="1" t="s">
@@ -5391,7 +5386,7 @@
       <c r="C176" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="E176" s="1" t="s">
+      <c r="E176" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F176" s="1" t="s">
@@ -5414,7 +5409,7 @@
       <c r="C177" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="E177" s="1" t="s">
+      <c r="E177" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F177" s="1" t="s">
@@ -5437,7 +5432,7 @@
       <c r="C178" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E178" s="1" t="s">
+      <c r="E178" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F178" s="1" t="s">
@@ -5460,7 +5455,7 @@
       <c r="C179" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="E179" s="1" t="s">
+      <c r="E179" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F179" s="1" t="s">
@@ -5483,7 +5478,7 @@
       <c r="C180" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E180" s="1" t="s">
+      <c r="E180" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F180" s="1" t="s">
@@ -5506,7 +5501,7 @@
       <c r="C181" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="E181" s="1" t="s">
+      <c r="E181" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F181" s="1" t="s">
@@ -5529,7 +5524,7 @@
       <c r="C182" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="E182" s="1" t="s">
+      <c r="E182" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F182" s="1" t="s">
@@ -5552,7 +5547,7 @@
       <c r="C183" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E183" s="1" t="s">
+      <c r="E183" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F183" s="1" t="s">
@@ -5575,7 +5570,7 @@
       <c r="C184" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="E184" s="1" t="s">
+      <c r="E184" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F184" s="1" t="s">
@@ -5598,7 +5593,7 @@
       <c r="C185" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E185" s="1" t="s">
+      <c r="E185" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F185" s="1" t="s">
@@ -5621,7 +5616,7 @@
       <c r="C186" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E186" s="1" t="s">
+      <c r="E186" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F186" s="1" t="s">
@@ -5644,7 +5639,7 @@
       <c r="C187" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E187" s="1" t="s">
+      <c r="E187" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F187" s="1" t="s">
@@ -5667,7 +5662,7 @@
       <c r="C188" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E188" s="1" t="s">
+      <c r="E188" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F188" s="1" t="s">
@@ -5690,7 +5685,7 @@
       <c r="C189" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E189" s="1" t="s">
+      <c r="E189" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F189" s="1" t="s">
@@ -5713,7 +5708,7 @@
       <c r="C190" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="E190" s="1" t="s">
+      <c r="E190" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F190" s="1" t="s">
@@ -5736,7 +5731,7 @@
       <c r="C191" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="E191" s="1" t="s">
+      <c r="E191" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F191" s="1" t="s">
@@ -5759,7 +5754,7 @@
       <c r="C192" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E192" s="1" t="s">
+      <c r="E192" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F192" s="1" t="s">
@@ -5782,7 +5777,7 @@
       <c r="C193" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="E193" s="1" t="s">
+      <c r="E193" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F193" s="1" t="s">
@@ -5805,7 +5800,7 @@
       <c r="C194" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="E194" s="1" t="s">
+      <c r="E194" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F194" s="1" t="s">
@@ -5828,7 +5823,7 @@
       <c r="C195" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="E195" s="1" t="s">
+      <c r="E195" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F195" s="1" t="s">
@@ -5851,7 +5846,7 @@
       <c r="C196" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="E196" s="1" t="s">
+      <c r="E196" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F196" s="1" t="s">
@@ -5874,7 +5869,7 @@
       <c r="C197" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="E197" s="1" t="s">
+      <c r="E197" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F197" s="1" t="s">
@@ -5897,7 +5892,7 @@
       <c r="C198" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="E198" s="1" t="s">
+      <c r="E198" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F198" s="1" t="s">
@@ -5920,7 +5915,7 @@
       <c r="C199" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="E199" s="1" t="s">
+      <c r="E199" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F199" s="1" t="s">
@@ -5943,7 +5938,7 @@
       <c r="C200" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E200" s="1" t="s">
+      <c r="E200" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F200" s="1" t="s">
@@ -5966,7 +5961,7 @@
       <c r="C201" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="E201" s="1" t="s">
+      <c r="E201" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F201" s="1" t="s">
@@ -5989,7 +5984,7 @@
       <c r="C202" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="E202" s="1" t="s">
+      <c r="E202" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F202" s="1" t="s">
@@ -6012,7 +6007,7 @@
       <c r="C203" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E203" s="1" t="s">
+      <c r="E203" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F203" s="1" t="s">
@@ -6035,7 +6030,7 @@
       <c r="C204" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="E204" s="1" t="s">
+      <c r="E204" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F204" s="1" t="s">
@@ -6058,7 +6053,7 @@
       <c r="C205" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E205" s="1" t="s">
+      <c r="E205" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F205" s="1" t="s">
@@ -6081,7 +6076,7 @@
       <c r="C206" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="E206" s="1" t="s">
+      <c r="E206" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F206" s="1" t="s">
@@ -6104,7 +6099,7 @@
       <c r="C207" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="E207" s="1" t="s">
+      <c r="E207" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F207" s="1" t="s">
@@ -6127,7 +6122,7 @@
       <c r="C208" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="E208" s="1" t="s">
+      <c r="E208" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F208" s="1" t="s">
@@ -6150,7 +6145,7 @@
       <c r="C209" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="E209" s="1" t="s">
+      <c r="E209" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F209" s="1" t="s">
@@ -6173,7 +6168,7 @@
       <c r="C210" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="E210" s="1" t="s">
+      <c r="E210" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F210" s="1" t="s">
@@ -6196,7 +6191,7 @@
       <c r="C211" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="E211" s="1" t="s">
+      <c r="E211" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F211" s="1" t="s">
@@ -6219,7 +6214,7 @@
       <c r="C212" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E212" s="1" t="s">
+      <c r="E212" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F212" s="1" t="s">
@@ -6242,7 +6237,7 @@
       <c r="C213" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="E213" s="1" t="s">
+      <c r="E213" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F213" s="1" t="s">
@@ -6265,7 +6260,7 @@
       <c r="C214" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="E214" s="1" t="s">
+      <c r="E214" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F214" s="1" t="s">
@@ -6288,7 +6283,7 @@
       <c r="C215" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E215" s="1" t="s">
+      <c r="E215" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F215" s="1" t="s">
@@ -6311,7 +6306,7 @@
       <c r="C216" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="E216" s="1" t="s">
+      <c r="E216" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F216" s="1" t="s">
@@ -6334,7 +6329,7 @@
       <c r="C217" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="E217" s="1" t="s">
+      <c r="E217" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F217" s="1" t="s">
@@ -6357,7 +6352,7 @@
       <c r="C218" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="E218" s="1" t="s">
+      <c r="E218" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F218" s="1" t="s">
@@ -6380,7 +6375,7 @@
       <c r="C219" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="E219" s="1" t="s">
+      <c r="E219" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F219" s="1" t="s">
@@ -6403,7 +6398,7 @@
       <c r="C220" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="E220" s="1" t="s">
+      <c r="E220" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F220" s="1" t="s">
@@ -6426,7 +6421,7 @@
       <c r="C221" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E221" s="1" t="s">
+      <c r="E221" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F221" s="1" t="s">
@@ -6449,7 +6444,7 @@
       <c r="C222" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="E222" s="1" t="s">
+      <c r="E222" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F222" s="1" t="s">
@@ -6472,7 +6467,7 @@
       <c r="C223" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="E223" s="1" t="s">
+      <c r="E223" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F223" s="1" t="s">
@@ -6495,7 +6490,7 @@
       <c r="C224" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="E224" s="1" t="s">
+      <c r="E224" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F224" s="1" t="s">
@@ -6518,7 +6513,7 @@
       <c r="C225" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="E225" s="1" t="s">
+      <c r="E225" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F225" s="1" t="s">
@@ -6541,7 +6536,7 @@
       <c r="C226" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E226" s="1" t="s">
+      <c r="E226" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F226" s="1" t="s">
@@ -6564,7 +6559,7 @@
       <c r="C227" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="E227" s="1" t="s">
+      <c r="E227" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F227" s="1" t="s">
@@ -6587,7 +6582,7 @@
       <c r="C228" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="E228" s="1" t="s">
+      <c r="E228" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F228" s="1" t="s">
@@ -6610,7 +6605,7 @@
       <c r="C229" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="E229" s="1" t="s">
+      <c r="E229" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F229" s="1" t="s">
@@ -6633,7 +6628,7 @@
       <c r="C230" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E230" s="1" t="s">
+      <c r="E230" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F230" s="1" t="s">
@@ -6656,7 +6651,7 @@
       <c r="C231" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="E231" s="1" t="s">
+      <c r="E231" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F231" s="1" t="s">
@@ -6679,7 +6674,7 @@
       <c r="C232" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="E232" s="1" t="s">
+      <c r="E232" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F232" s="1" t="s">
@@ -6702,7 +6697,7 @@
       <c r="C233" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E233" s="1" t="s">
+      <c r="E233" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F233" s="1" t="s">
@@ -6725,7 +6720,7 @@
       <c r="C234" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="E234" s="1" t="s">
+      <c r="E234" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F234" s="1" t="s">
@@ -6748,7 +6743,7 @@
       <c r="C235" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="E235" s="1" t="s">
+      <c r="E235" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F235" s="1" t="s">
@@ -6771,7 +6766,7 @@
       <c r="C236" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="E236" s="1" t="s">
+      <c r="E236" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F236" s="1" t="s">
@@ -6794,7 +6789,7 @@
       <c r="C237" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="E237" s="1" t="s">
+      <c r="E237" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F237" s="1" t="s">
@@ -6817,7 +6812,7 @@
       <c r="C238" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="E238" s="1" t="s">
+      <c r="E238" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F238" s="1" t="s">
@@ -6840,7 +6835,7 @@
       <c r="C239" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="E239" s="1" t="s">
+      <c r="E239" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F239" s="1" t="s">
@@ -6863,7 +6858,7 @@
       <c r="C240" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E240" s="1" t="s">
+      <c r="E240" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F240" s="1" t="s">
@@ -6886,7 +6881,7 @@
       <c r="C241" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E241" s="1" t="s">
+      <c r="E241" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F241" s="1" t="s">
@@ -6909,7 +6904,7 @@
       <c r="C242" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="E242" s="1" t="s">
+      <c r="E242" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F242" s="1" t="s">
@@ -6932,7 +6927,7 @@
       <c r="C243" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E243" s="1" t="s">
+      <c r="E243" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F243" s="1" t="s">
@@ -6955,7 +6950,7 @@
       <c r="C244" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E244" s="1" t="s">
+      <c r="E244" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F244" s="1" t="s">
@@ -6978,7 +6973,7 @@
       <c r="C245" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="E245" s="1" t="s">
+      <c r="E245" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F245" s="1" t="s">
@@ -7001,7 +6996,7 @@
       <c r="C246" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="E246" s="1" t="s">
+      <c r="E246" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F246" s="1" t="s">
@@ -7024,7 +7019,7 @@
       <c r="C247" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="E247" s="1" t="s">
+      <c r="E247" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F247" s="1" t="s">
@@ -7047,7 +7042,7 @@
       <c r="C248" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="E248" s="1" t="s">
+      <c r="E248" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F248" s="1" t="s">
@@ -7070,7 +7065,7 @@
       <c r="C249" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="E249" s="1" t="s">
+      <c r="E249" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F249" s="1" t="s">
@@ -7093,7 +7088,7 @@
       <c r="C250" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="E250" s="1" t="s">
+      <c r="E250" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F250" s="1" t="s">
@@ -7116,7 +7111,7 @@
       <c r="C251" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="E251" s="1" t="s">
+      <c r="E251" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F251" s="1" t="s">
@@ -7139,7 +7134,7 @@
       <c r="C252" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="E252" s="1" t="s">
+      <c r="E252" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F252" s="1" t="s">
@@ -7162,7 +7157,7 @@
       <c r="C253" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="E253" s="1" t="s">
+      <c r="E253" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F253" s="1" t="s">
@@ -7185,7 +7180,7 @@
       <c r="C254" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="E254" s="1" t="s">
+      <c r="E254" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F254" s="1" t="s">
@@ -7208,7 +7203,7 @@
       <c r="C255" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="E255" s="1" t="s">
+      <c r="E255" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F255" s="1" t="s">
@@ -7231,7 +7226,7 @@
       <c r="C256" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="E256" s="1" t="s">
+      <c r="E256" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F256" s="1" t="s">
@@ -7254,7 +7249,7 @@
       <c r="C257" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="E257" s="1" t="s">
+      <c r="E257" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F257" s="1" t="s">
@@ -7277,7 +7272,7 @@
       <c r="C258" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E258" s="1" t="s">
+      <c r="E258" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F258" s="1" t="s">
@@ -7300,7 +7295,7 @@
       <c r="C259" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="E259" s="1" t="s">
+      <c r="E259" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F259" s="1" t="s">
@@ -7323,7 +7318,7 @@
       <c r="C260" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E260" s="1" t="s">
+      <c r="E260" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F260" s="1" t="s">
@@ -7346,7 +7341,7 @@
       <c r="C261" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="E261" s="1" t="s">
+      <c r="E261" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F261" s="1" t="s">
@@ -7369,7 +7364,7 @@
       <c r="C262" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="E262" s="1" t="s">
+      <c r="E262" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F262" s="1" t="s">
@@ -7392,7 +7387,7 @@
       <c r="C263" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="E263" s="1" t="s">
+      <c r="E263" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F263" s="1" t="s">
@@ -7415,7 +7410,7 @@
       <c r="C264" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="E264" s="1" t="s">
+      <c r="E264" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F264" s="1" t="s">
@@ -7438,7 +7433,7 @@
       <c r="C265" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="E265" s="1" t="s">
+      <c r="E265" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F265" s="1" t="s">
@@ -7461,7 +7456,7 @@
       <c r="C266" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="E266" s="1" t="s">
+      <c r="E266" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F266" s="1" t="s">
@@ -7484,7 +7479,7 @@
       <c r="C267" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="E267" s="1" t="s">
+      <c r="E267" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F267" s="1" t="s">
@@ -7507,7 +7502,7 @@
       <c r="C268" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="E268" s="1" t="s">
+      <c r="E268" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F268" s="1" t="s">
@@ -7530,7 +7525,7 @@
       <c r="C269" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="E269" s="1" t="s">
+      <c r="E269" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F269" s="1" t="s">
@@ -7553,7 +7548,7 @@
       <c r="C270" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="E270" s="1" t="s">
+      <c r="E270" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F270" s="1" t="s">
@@ -7576,7 +7571,7 @@
       <c r="C271" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="E271" s="1" t="s">
+      <c r="E271" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F271" s="1" t="s">
@@ -7599,7 +7594,7 @@
       <c r="C272" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="E272" s="1" t="s">
+      <c r="E272" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F272" s="1" t="s">
@@ -7622,7 +7617,7 @@
       <c r="C273" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="E273" s="1" t="s">
+      <c r="E273" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F273" s="1" t="s">
@@ -7645,7 +7640,7 @@
       <c r="C274" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="E274" s="1" t="s">
+      <c r="E274" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F274" s="1" t="s">
@@ -7668,7 +7663,7 @@
       <c r="C275" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="E275" s="1" t="s">
+      <c r="E275" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F275" s="1" t="s">
@@ -7691,7 +7686,7 @@
       <c r="C276" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E276" s="1" t="s">
+      <c r="E276" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F276" s="1" t="s">
@@ -7714,7 +7709,7 @@
       <c r="C277" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="E277" s="1" t="s">
+      <c r="E277" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F277" s="1" t="s">
@@ -7737,7 +7732,7 @@
       <c r="C278" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="E278" s="1" t="s">
+      <c r="E278" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F278" s="1" t="s">
@@ -7760,7 +7755,7 @@
       <c r="C279" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="E279" s="1" t="s">
+      <c r="E279" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F279" s="1" t="s">
@@ -7783,7 +7778,7 @@
       <c r="C280" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E280" s="1" t="s">
+      <c r="E280" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F280" s="1" t="s">
@@ -7806,7 +7801,7 @@
       <c r="C281" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="E281" s="1" t="s">
+      <c r="E281" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F281" s="1" t="s">
@@ -7829,7 +7824,7 @@
       <c r="C282" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="E282" s="1" t="s">
+      <c r="E282" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F282" s="1" t="s">
@@ -7852,7 +7847,7 @@
       <c r="C283" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="E283" s="1" t="s">
+      <c r="E283" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F283" s="1" t="s">
@@ -7875,7 +7870,7 @@
       <c r="C284" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="E284" s="1" t="s">
+      <c r="E284" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F284" s="1" t="s">
@@ -7898,7 +7893,7 @@
       <c r="C285" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="E285" s="1" t="s">
+      <c r="E285" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F285" s="1" t="s">
@@ -7921,7 +7916,7 @@
       <c r="C286" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="E286" s="1" t="s">
+      <c r="E286" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F286" s="1" t="s">
@@ -7944,7 +7939,7 @@
       <c r="C287" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="E287" s="1" t="s">
+      <c r="E287" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F287" s="1" t="s">
@@ -7967,7 +7962,7 @@
       <c r="C288" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="E288" s="1" t="s">
+      <c r="E288" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F288" s="1" t="s">
@@ -7990,7 +7985,7 @@
       <c r="C289" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="E289" s="1" t="s">
+      <c r="E289" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F289" s="1" t="s">
@@ -8013,7 +8008,7 @@
       <c r="C290" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="E290" s="1" t="s">
+      <c r="E290" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F290" s="1" t="s">
@@ -8036,7 +8031,7 @@
       <c r="C291" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="E291" s="1" t="s">
+      <c r="E291" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F291" s="1" t="s">
@@ -8059,7 +8054,7 @@
       <c r="C292" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="E292" s="1" t="s">
+      <c r="E292" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F292" s="1" t="s">
@@ -8082,7 +8077,7 @@
       <c r="C293" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="E293" s="1" t="s">
+      <c r="E293" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F293" s="1" t="s">
@@ -8105,7 +8100,7 @@
       <c r="C294" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="E294" s="1" t="s">
+      <c r="E294" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F294" s="1" t="s">
@@ -8128,7 +8123,7 @@
       <c r="C295" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="E295" s="1" t="s">
+      <c r="E295" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F295" s="1" t="s">
@@ -8151,7 +8146,7 @@
       <c r="C296" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="E296" s="1" t="s">
+      <c r="E296" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F296" s="1" t="s">
@@ -8174,7 +8169,7 @@
       <c r="C297" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="E297" s="1" t="s">
+      <c r="E297" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F297" s="1" t="s">
@@ -8197,7 +8192,7 @@
       <c r="C298" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="E298" s="1" t="s">
+      <c r="E298" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F298" s="1" t="s">
@@ -8220,7 +8215,7 @@
       <c r="C299" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="E299" s="1" t="s">
+      <c r="E299" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F299" s="1" t="s">
@@ -8243,7 +8238,7 @@
       <c r="C300" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="E300" s="1" t="s">
+      <c r="E300" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F300" s="1" t="s">
@@ -8255,6 +8250,186 @@
       <c r="O300" s="1" t="s">
         <v>19</v>
       </c>
+    </row>
+    <row r="301" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E301" s="3"/>
+    </row>
+    <row r="302" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E302" s="3"/>
+    </row>
+    <row r="303" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E303" s="3"/>
+    </row>
+    <row r="304" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E304" s="3"/>
+    </row>
+    <row r="305" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E305" s="3"/>
+    </row>
+    <row r="306" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E306" s="3"/>
+    </row>
+    <row r="307" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E307" s="3"/>
+    </row>
+    <row r="308" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E308" s="3"/>
+    </row>
+    <row r="309" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E309" s="3"/>
+    </row>
+    <row r="310" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E310" s="3"/>
+    </row>
+    <row r="311" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E311" s="3"/>
+    </row>
+    <row r="312" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E312" s="3"/>
+    </row>
+    <row r="313" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E313" s="3"/>
+    </row>
+    <row r="314" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E314" s="3"/>
+    </row>
+    <row r="315" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E315" s="3"/>
+    </row>
+    <row r="316" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E316" s="3"/>
+    </row>
+    <row r="317" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E317" s="3"/>
+    </row>
+    <row r="318" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E318" s="3"/>
+    </row>
+    <row r="319" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E319" s="3"/>
+    </row>
+    <row r="320" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E320" s="3"/>
+    </row>
+    <row r="321" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E321" s="3"/>
+    </row>
+    <row r="322" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E322" s="3"/>
+    </row>
+    <row r="323" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E323" s="3"/>
+    </row>
+    <row r="324" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E324" s="3"/>
+    </row>
+    <row r="325" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E325" s="3"/>
+    </row>
+    <row r="326" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E326" s="3"/>
+    </row>
+    <row r="327" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E327" s="3"/>
+    </row>
+    <row r="328" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E328" s="3"/>
+    </row>
+    <row r="329" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E329" s="3"/>
+    </row>
+    <row r="330" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E330" s="3"/>
+    </row>
+    <row r="331" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E331" s="3"/>
+    </row>
+    <row r="332" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E332" s="3"/>
+    </row>
+    <row r="333" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E333" s="3"/>
+    </row>
+    <row r="334" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E334" s="3"/>
+    </row>
+    <row r="335" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E335" s="3"/>
+    </row>
+    <row r="336" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E336" s="3"/>
+    </row>
+    <row r="337" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E337" s="3"/>
+    </row>
+    <row r="338" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E338" s="3"/>
+    </row>
+    <row r="339" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E339" s="3"/>
+    </row>
+    <row r="340" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E340" s="3"/>
+    </row>
+    <row r="341" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E341" s="3"/>
+    </row>
+    <row r="342" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E342" s="3"/>
+    </row>
+    <row r="343" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E343" s="3"/>
+    </row>
+    <row r="344" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E344" s="3"/>
+    </row>
+    <row r="345" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E345" s="3"/>
+    </row>
+    <row r="346" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E346" s="3"/>
+    </row>
+    <row r="347" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E347" s="3"/>
+    </row>
+    <row r="348" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E348" s="3"/>
+    </row>
+    <row r="349" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E349" s="3"/>
+    </row>
+    <row r="350" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E350" s="3"/>
+    </row>
+    <row r="351" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E351" s="3"/>
+    </row>
+    <row r="352" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E352" s="3"/>
+    </row>
+    <row r="353" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E353" s="3"/>
+    </row>
+    <row r="354" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E354" s="3"/>
+    </row>
+    <row r="355" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E355" s="3"/>
+    </row>
+    <row r="356" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E356" s="3"/>
+    </row>
+    <row r="357" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E357" s="3"/>
+    </row>
+    <row r="358" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E358" s="3"/>
+    </row>
+    <row r="359" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E359" s="3"/>
+    </row>
+    <row r="360" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E360" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
